--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/auth-service/login-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/auth-service/login-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="100">
-  <si>
-    <t>Statement: AuthService.login(data) – Looks up user by email via userRepository.findByEmail(). Throws NotFoundError if user not found (anti-enumeration message). Compares password with bcrypt. Throws AuthorizationError if password wrong (same anti-enumeration message). Returns SessionData on success with role-specific fields (adminId, memberId, isActive).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="45">
+  <si>
+    <t>Statement: AuthService.login(data) – Authenticates user.</t>
   </si>
   <si>
     <t/>
@@ -37,20 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>userRepository is accessible</t>
+    <t>userRepository accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;SessionData&gt;  OR  throws NotFoundError / AuthorizationError</t>
+    <t>Output: Promise&lt;SessionData&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: returns SessionData with userId, email, fullName, role, optional memberId/adminId/isActive.
-On error: no state change.</t>
+    <t>Session data returned.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -65,46 +64,13 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>email lookup</t>
-  </si>
-  <si>
-    <t>user with given email exists in repository</t>
-  </si>
-  <si>
-    <t>no user found for email → throws NotFoundError("Invalid email or password")</t>
-  </si>
-  <si>
-    <t>password check</t>
-  </si>
-  <si>
-    <t>bcrypt.compare returns true</t>
-  </si>
-  <si>
-    <t>bcrypt.compare returns false → throws AuthorizationError("Invalid email or password")</t>
-  </si>
-  <si>
-    <t>error message</t>
-  </si>
-  <si>
-    <t>same message for both failure cases (anti-enumeration)</t>
-  </si>
-  <si>
-    <t>session data</t>
-  </si>
-  <si>
-    <t>admin credentials → adminId populated</t>
-  </si>
-  <si>
-    <t>member credentials → memberId + isActive populated</t>
-  </si>
-  <si>
-    <t>isActive flag</t>
-  </si>
-  <si>
-    <t>active member → isActive=true</t>
-  </si>
-  <si>
-    <t>inactive member → isActive=false</t>
+    <t>Credentials</t>
+  </si>
+  <si>
+    <t>Correct</t>
+  </si>
+  <si>
+    <t>Wrong</t>
   </si>
   <si>
     <t>No TC</t>
@@ -122,87 +88,12 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>findByEmail returns null</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError("Invalid email or password")</t>
-  </si>
-  <si>
-    <t>2,5</t>
-  </si>
-  <si>
-    <t>Error message is "Invalid email or password" (anti-enumeration)</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Email found, bcrypt.compare returns false</t>
-  </si>
-  <si>
-    <t>Throws AuthorizationError("Invalid email or password")</t>
-  </si>
-  <si>
-    <t>4,5</t>
-  </si>
-  <si>
-    <t>Email found, wrong password</t>
-  </si>
-  <si>
-    <t>Same message "Invalid email or password"</t>
-  </si>
-  <si>
-    <t>1,3,6</t>
-  </si>
-  <si>
-    <t>Admin credentials, bcrypt returns true</t>
-  </si>
-  <si>
-    <t>SessionData with adminId="admin-001", no memberId</t>
-  </si>
-  <si>
-    <t>1,3,7,8</t>
-  </si>
-  <si>
-    <t>Member credentials, bcrypt returns true</t>
-  </si>
-  <si>
-    <t>SessionData with memberId="member-001", isActive=true</t>
-  </si>
-  <si>
-    <t>1,3,7</t>
-  </si>
-  <si>
-    <t>Member credentials (fullName check)</t>
-  </si>
-  <si>
-    <t>SessionData.fullName populated correctly</t>
-  </si>
-  <si>
-    <t>1,3,7,9</t>
-  </si>
-  <si>
-    <t>Inactive member credentials, bcrypt true</t>
-  </si>
-  <si>
-    <t>SessionData.isActive=false, memberId populated</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>No numerical boundaries – email/password are opaque strings at service layer</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
@@ -212,73 +103,13 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Non-existent email</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Error msg = "Invalid email or password"</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Correct email, wrong password</t>
-  </si>
-  <si>
-    <t>Throws AuthorizationError</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Wrong password failure path</t>
-  </si>
-  <si>
-    <t>Same error message (anti-enumeration)</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Admin credentials</t>
-  </si>
-  <si>
-    <t>Returns SessionData with adminId</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
-    <t>Active member credentials</t>
-  </si>
-  <si>
-    <t>Returns SessionData with memberId, isActive=true</t>
-  </si>
-  <si>
-    <t>EP-7</t>
-  </si>
-  <si>
-    <t>Member credentials (fullName)</t>
-  </si>
-  <si>
-    <t>fullName populated</t>
-  </si>
-  <si>
-    <t>EP-8</t>
-  </si>
-  <si>
-    <t>Inactive member credentials</t>
-  </si>
-  <si>
-    <t>isActive=false returned</t>
+    <t>Login test</t>
+  </si>
+  <si>
+    <t>Success/Error</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -314,10 +145,13 @@
     <t>AUTH-01</t>
   </si>
   <si>
-    <t>Bug: if (!user) threw AuthorizationError instead of NotFoundError — corrected to throw NotFoundError("Invalid email or password")</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>not yet</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -833,7 +667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -866,119 +700,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -989,7 +711,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1001,155 +723,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +746,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1170,24 +756,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1210,19 +785,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1233,7 +808,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1246,22 +821,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1269,19 +844,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1289,19 +864,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1309,19 +884,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1329,19 +904,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1349,19 +924,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1369,19 +944,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,19 +964,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1409,19 +984,79 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>86</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1449,16 +1084,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1466,66 +1101,66 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="H3" s="1">
-        <v>8</v>
-      </c>
-      <c r="I3" s="1">
-        <v>8</v>
-      </c>
-      <c r="J3" s="1">
         <v>0</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/auth-service/login-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/auth-service/login-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="45">
-  <si>
-    <t>Statement: AuthService.login(data) – Authenticates user.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="84">
+  <si>
+    <t>Statement: AuthService.login(data) – Validates user credentials. Looks up the user by email, compares the provided password against the stored hash. Returns a SessionData object on success. Throws NotFoundError if no user exists with the given email. Throws AuthorizationError if the password does not match.</t>
   </si>
   <si>
     <t/>
@@ -37,7 +37,7 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>userRepository accessible</t>
+    <t>Input data is provided. User with the given email may or may not exist in the system.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Session data returned.</t>
+    <t>On success: SessionData returned with userId, email, fullName, role, and role-specific profile fields. On failure: NotFoundError or AuthorizationError thrown with message "Invalid email or password".</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,13 +64,37 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Credentials</t>
-  </si>
-  <si>
-    <t>Correct</t>
-  </si>
-  <si>
-    <t>Wrong</t>
+    <t>Credentials validity (Admin)</t>
+  </si>
+  <si>
+    <t>Registered admin email + correct password → SessionData with adminId set, memberId undefined</t>
+  </si>
+  <si>
+    <t>Credentials validity (Member)</t>
+  </si>
+  <si>
+    <t>Registered member email + correct password → SessionData with memberId set, isActive: true</t>
+  </si>
+  <si>
+    <t>Member active status</t>
+  </si>
+  <si>
+    <t>Active member → isActive: true in SessionData</t>
+  </si>
+  <si>
+    <t>Inactive member → isActive: false in SessionData</t>
+  </si>
+  <si>
+    <t>User existence</t>
+  </si>
+  <si>
+    <t>Unregistered email → NotFoundError("Invalid email or password")</t>
+  </si>
+  <si>
+    <t>Password correctness</t>
+  </si>
+  <si>
+    <t>Wrong password → AuthorizationError("Invalid email or password")</t>
   </si>
   <si>
     <t>No TC</t>
@@ -88,28 +112,121 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>email: admin@gymtrackerpro.com, password: CorrectPass1!</t>
+  </si>
+  <si>
+    <t>SessionData returned: role Admin, userId and adminId set, memberId undefined, isActive undefined</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>email: member@example.com, password: CorrectPass1!</t>
+  </si>
+  <si>
+    <t>SessionData returned: role Member, memberId set, adminId undefined, isActive: true</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>email: member@example.com, password: CorrectPass1! (inactive user)</t>
+  </si>
+  <si>
+    <t>SessionData returned: role Member, memberId set, isActive: false</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>email: unknown@example.com, password: AnyPassword1!</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Invalid email or password")</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>email: member@example.com, password: WrongPassword1!</t>
+  </si>
+  <si>
+    <t>throws AuthorizationError("Invalid email or password")</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>Email length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>Password length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, no match), 1 char (no match), 1 char (match)</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>email: "" (no user found)</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>email: "a" (no user found)</t>
+  </si>
+  <si>
+    <t>email: "a" (user found, correct pass)</t>
+  </si>
+  <si>
+    <t>SessionData returned with email: "a"</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=0)</t>
+  </si>
+  <si>
+    <t>password: "" (hash does not match)</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=1)</t>
+  </si>
+  <si>
+    <t>password: "p" (hash does not match)</t>
+  </si>
+  <si>
+    <t>password: "p" (hash matches)</t>
+  </si>
+  <si>
+    <t>SessionData returned</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Login test</t>
-  </si>
-  <si>
-    <t>Success/Error</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>BVA-1</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
   </si>
   <si>
     <t>Testing</t>
@@ -142,7 +259,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-01</t>
+    <t>SERV-01</t>
   </si>
   <si>
     <t>n/a</t>
@@ -667,7 +784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -700,7 +817,77 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -711,7 +898,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -723,19 +910,104 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -756,13 +1028,35 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -785,19 +1079,121 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -821,22 +1217,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -844,19 +1240,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -864,19 +1260,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -884,19 +1280,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -904,19 +1300,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -924,19 +1320,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -944,19 +1340,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -964,19 +1360,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -984,19 +1380,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1004,19 +1400,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1024,19 +1420,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1044,19 +1440,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1084,16 +1480,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1101,39 +1497,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="B3" s="1">
         <v>11</v>
@@ -1148,19 +1544,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
